--- a/stories/arbres/TREE-SEC-007.xlsx
+++ b/stories/arbres/TREE-SEC-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo joue avec Papa, dans la cuisine. Papa montre l'espace. Kenzo joue dans l'espace montré. Papa, l'adulte, voit. Les pieds restent dans cet espace. Les mains jouent ici. Maman coupe le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom vient jouer. Papa montre l'espace, près de la table. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Le pain craque. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Un oiseau chante dehors. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. La cuillère tinte. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le tapis est doux. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. L'eau coule. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. La cuillère tinte. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le tapis est doux. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Ça sent la soupe. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Un oiseau chante dehors. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5307,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5474,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5641,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5808,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5975,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6142,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6309,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6476,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa vient jouer. Papa montre l'espace, près du tapis. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. La cuillère tinte. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7383,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7550,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. La cuillère tinte. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7717,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7884,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le tapis est doux. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8051,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8218,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Ça sent la soupe. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8385,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8552,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Le tapis est doux. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8743,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8910,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9077,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9244,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9411,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9578,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9745,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9912,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Ça sent la soupe. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10103,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10270,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Ça sent la soupe. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10437,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10604,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le pain craque. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10771,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10938,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. L'eau coule. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11105,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11272,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami vient jouer. Papa montre l'espace, près du banc. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11457,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11630,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11499,6 +11821,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11661,6 +11988,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Le pain craque. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12179,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12346,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12513,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12680,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12847,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13014,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13181,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13348,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. L'eau coule. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13539,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13706,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Ça sent la soupe. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13873,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14040,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le pain craque. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14207,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14374,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. L'eau coule. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14541,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14708,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Un oiseau chante dehors. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14899,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15066,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le pain craque. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15233,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15400,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. L'eau coule. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15567,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15734,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Un oiseau chante dehors. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15901,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15494,6 +15941,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-007.xlsx
+++ b/stories/arbres/TREE-SEC-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Kenzo joue avec Papa, dans la cuisine. Papa montre l'espace. Kenzo joue dans l'espace montré. Papa, l'adulte, voit. Les pieds restent dans cet espace. Les mains jouent ici. Maman coupe le pain.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Tom vient jouer. Papa montre l'espace, près de la table. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Le pain craque. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|Kenzo prend une pomme. Un oiseau chante dehors. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|Kenzo prend un yaourt. La cuillère tinte. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le tapis est doux. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Kenzo a choisi le livre. L'eau coule. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|Kenzo prend une pomme. La cuillère tinte. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le tapis est doux. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Ça sent la soupe. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Un oiseau chante dehors. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5312,6 +5340,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5479,6 +5508,7 @@
           <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5646,6 +5676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5813,6 +5844,7 @@
           <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5980,6 +6012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6147,6 +6180,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6314,6 +6348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
           <t>narrateur|Léa vient jouer. Papa montre l'espace, près du tapis. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Kenzo a choisi les cubes. La cuillère tinte. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7388,6 +7428,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7555,6 +7596,7 @@
           <t>narrateur|Kenzo prend une pomme. La cuillère tinte. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7722,6 +7764,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7889,6 +7932,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le tapis est doux. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8056,6 +8100,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8223,6 +8268,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Ça sent la soupe. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8390,6 +8436,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8557,6 +8604,7 @@
           <t>narrateur|Kenzo a choisi le livre. Le tapis est doux. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8748,6 +8796,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8915,6 +8964,7 @@
           <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9082,6 +9132,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9249,6 +9300,7 @@
           <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9416,6 +9468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9583,6 +9636,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9750,6 +9804,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9917,6 +9972,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Ça sent la soupe. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10108,6 +10164,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10275,6 +10332,7 @@
           <t>narrateur|Kenzo prend une pomme. Ça sent la soupe. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10500,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10609,6 +10668,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le pain craque. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10776,6 +10836,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10943,6 +11004,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. L'eau coule. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11110,6 +11172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11277,6 +11340,7 @@
           <t>narrateur|Sami vient jouer. Papa montre l'espace, près du banc. Kenzo joue dans l'espace montré. L'adulte voit. Pieds ici. Mains ici.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11464,6 +11528,7 @@
           <t>narrateur|On joue où ? Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11635,6 +11700,7 @@
           <t>narrateur|Oui. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo retient : espace montré, adulte voit. Les mains jouent ici, dans l'espace montré. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11826,6 +11892,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11993,6 +12060,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Le pain craque. Ils prennent les cubes. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12184,6 +12252,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12351,6 +12420,7 @@
           <t>narrateur|Kenzo prend une pomme. Le tapis est doux. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12518,6 +12588,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12685,6 +12756,7 @@
           <t>narrateur|Kenzo prend un yaourt. Ça sent la soupe. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12852,6 +12924,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13019,6 +13092,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le pain craque. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13186,6 +13260,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13353,6 +13428,7 @@
           <t>narrateur|Kenzo a choisi le livre. L'eau coule. Ils prennent le livre. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13544,6 +13620,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13711,6 +13788,7 @@
           <t>narrateur|Kenzo prend une pomme. Ça sent la soupe. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13878,6 +13956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14045,6 +14124,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le pain craque. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14212,6 +14292,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14379,6 +14460,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. L'eau coule. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14546,6 +14628,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14713,6 +14796,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Un oiseau chante dehors. Ils prennent la dînette. Dans l'espace montré. Papa, l'adulte, voit. Les mains jouent ici, dans l'espace montré. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14904,6 +14988,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15071,6 +15156,7 @@
           <t>narrateur|Kenzo prend une pomme. Le pain craque. Maman tend une pomme. Kenzo reste dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15238,6 +15324,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15405,6 +15492,7 @@
           <t>narrateur|Kenzo prend un yaourt. L'eau coule. Maman tend un yaourt. L'adulte voit Kenzo. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15572,6 +15660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15739,6 +15828,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Un oiseau chante dehors. Maman tend un morceau de pain. Pieds dans l'espace montré. On joue dans l'espace montré. L'adulte voit. Les pieds restent dans cet espace. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15906,6 +15996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15924,7 +16015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15948,6 +16039,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15962,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16149,6 +16254,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
